--- a/タイムカード入力空バージョン.xlsx
+++ b/タイムカード入力空バージョン.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ef1d1f3ca849450/ドキュメント/Antigravity_products/timecard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{524A11A4-0B7F-4C6A-924A-7794EB9FADAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B842637-59DB-4685-ACCA-B482C0D7D2AA}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{524A11A4-0B7F-4C6A-924A-7794EB9FADAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2E999A3-109B-4142-872C-4934C1804E5E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="648" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="マスタ" sheetId="16" r:id="rId1"/>
@@ -502,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -547,9 +547,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3019,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -3040,7 +3037,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -3057,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -3078,7 +3075,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -3095,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -3116,7 +3113,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -3133,7 +3130,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -3154,7 +3151,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -3171,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -3209,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -3230,7 +3227,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -3247,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -3268,7 +3265,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -3285,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -3306,7 +3303,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -3323,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -3344,7 +3341,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -3361,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -3382,7 +3379,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -3399,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -3420,7 +3417,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -3437,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -3458,7 +3455,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -3475,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -3496,7 +3493,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -3513,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -3534,7 +3531,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -3551,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -3572,7 +3569,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -3589,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -3610,7 +3607,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -3627,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -3648,7 +3645,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -3665,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -3686,7 +3683,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -3703,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -3724,7 +3721,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -3741,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -3762,7 +3759,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -3779,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -3800,7 +3797,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -3817,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -3838,7 +3835,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -3855,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -3876,7 +3873,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -3893,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -3914,7 +3911,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -3931,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -3952,7 +3949,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -3969,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -3990,7 +3987,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -4007,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -4028,7 +4025,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -4045,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -4064,7 +4061,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -4081,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -4100,7 +4097,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -4117,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -4136,7 +4133,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -4153,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -4372,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -4393,7 +4390,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -4410,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -4431,7 +4428,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -4448,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -4469,7 +4466,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -4486,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -4507,7 +4504,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -4524,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -4562,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -4583,7 +4580,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -4600,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -4621,7 +4618,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -4638,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -4659,7 +4656,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -4676,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -4697,7 +4694,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -4714,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -4735,7 +4732,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -4752,7 +4749,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -4773,7 +4770,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -4790,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -4811,7 +4808,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -4828,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -4849,7 +4846,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -4866,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -4887,7 +4884,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -4904,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -4925,7 +4922,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -4942,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -4963,7 +4960,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -4980,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -5001,7 +4998,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -5018,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -5039,7 +5036,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -5056,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -5077,7 +5074,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -5094,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -5115,7 +5112,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -5132,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -5153,7 +5150,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -5170,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -5191,7 +5188,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -5208,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -5229,7 +5226,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -5246,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -5267,7 +5264,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -5284,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -5305,7 +5302,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -5322,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -5343,7 +5340,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -5360,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -5381,7 +5378,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -5398,7 +5395,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -5417,7 +5414,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -5434,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -5453,7 +5450,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -5470,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -5489,7 +5486,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -5506,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -5730,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -5751,7 +5748,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -5768,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -5789,7 +5786,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -5806,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -5827,7 +5824,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -5844,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -5865,7 +5862,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -5882,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -5920,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -5941,7 +5938,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -5958,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -5979,7 +5976,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -5996,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -6017,7 +6014,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -6034,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -6055,7 +6052,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -6072,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -6093,7 +6090,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -6110,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -6131,7 +6128,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -6148,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -6169,7 +6166,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -6186,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -6207,7 +6204,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -6224,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -6245,7 +6242,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -6262,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -6283,7 +6280,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -6300,7 +6297,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -6321,7 +6318,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -6338,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -6359,7 +6356,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -6376,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -6397,7 +6394,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -6414,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -6435,7 +6432,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -6452,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -6473,7 +6470,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -6490,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -6511,7 +6508,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -6528,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -6549,7 +6546,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -6566,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -6587,7 +6584,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -6604,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -6625,7 +6622,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -6642,7 +6639,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -6663,7 +6660,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -6680,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -6701,7 +6698,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -6718,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -6739,7 +6736,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -6756,7 +6753,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -6775,7 +6772,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -6792,7 +6789,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -6811,7 +6808,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -6828,7 +6825,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -6847,7 +6844,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -6864,7 +6861,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -7085,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -7106,7 +7103,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -7123,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -7144,7 +7141,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -7161,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -7182,7 +7179,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -7199,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -7220,7 +7217,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -7237,7 +7234,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -7275,7 +7272,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -7296,7 +7293,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -7313,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -7334,7 +7331,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -7351,7 +7348,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -7372,7 +7369,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -7389,7 +7386,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -7410,7 +7407,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -7427,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -7448,7 +7445,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -7465,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -7486,7 +7483,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -7503,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -7524,7 +7521,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -7541,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -7562,7 +7559,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -7579,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -7600,7 +7597,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -7617,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -7638,7 +7635,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -7655,7 +7652,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -7676,7 +7673,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -7693,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -7714,7 +7711,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -7731,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -7752,7 +7749,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -7769,7 +7766,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -7790,7 +7787,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -7807,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -7828,7 +7825,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -7845,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -7866,7 +7863,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -7883,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -7904,7 +7901,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -7921,7 +7918,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -7942,7 +7939,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -7959,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -7980,7 +7977,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -7997,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -8018,7 +8015,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -8035,7 +8032,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -8056,7 +8053,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -8073,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -8094,7 +8091,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -8111,7 +8108,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -8130,7 +8127,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -8147,7 +8144,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -8166,7 +8163,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -8183,7 +8180,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -8202,7 +8199,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -8219,7 +8216,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -8431,7 +8428,8 @@
         <f t="shared" ref="J2:J32" si="1">F2-C2-(E2-D2)</f>
         <v>0</v>
       </c>
-      <c r="K2" s="30">
+      <c r="K2" s="8">
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -8452,7 +8450,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -8469,7 +8467,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -8490,7 +8488,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -8507,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -8528,7 +8526,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -8545,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -8566,7 +8564,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -8583,7 +8581,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -8621,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -8642,7 +8640,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -8659,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -8680,7 +8678,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -8697,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -8718,7 +8716,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -8735,7 +8733,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -8756,7 +8754,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -8773,7 +8771,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -8794,7 +8792,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -8811,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -8832,7 +8830,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -8849,7 +8847,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -8870,7 +8868,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -8887,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -8908,7 +8906,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -8925,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -8946,7 +8944,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -8963,7 +8961,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -8984,7 +8982,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -9001,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -9022,7 +9020,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -9039,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -9060,7 +9058,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -9077,7 +9075,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -9098,7 +9096,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -9115,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -9136,7 +9134,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -9153,7 +9151,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -9174,7 +9172,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -9191,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -9212,7 +9210,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -9229,7 +9227,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -9250,7 +9248,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -9267,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -9288,7 +9286,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -9305,7 +9303,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -9326,7 +9324,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -9343,7 +9341,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -9364,7 +9362,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -9381,7 +9379,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -9402,7 +9400,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -9419,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -9440,7 +9438,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -9457,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -9476,7 +9474,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -9493,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -9512,7 +9510,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -9529,7 +9527,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -9548,7 +9546,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -9565,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -9588,10 +9586,10 @@
       <c r="B33" s="27">
         <v>0</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="32"/>
+      <c r="D33" s="31"/>
       <c r="E33" s="27" t="s">
         <v>25</v>
       </c>
@@ -9616,8 +9614,8 @@
       </c>
     </row>
     <row r="34" spans="1:14" ht="18.600000000000001" thickBot="1">
-      <c r="C34" s="31"/>
-      <c r="D34" s="32"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="31"/>
       <c r="E34" s="28"/>
       <c r="G34" s="19">
         <f>SUM(G2:G32)</f>
@@ -9653,8 +9651,8 @@
       <c r="G35" s="24"/>
     </row>
     <row r="36" spans="1:14" ht="18.600000000000001" thickBot="1">
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
       <c r="G36" s="24"/>
       <c r="L36" s="2">
         <f>L34*12/52</f>
@@ -9811,7 +9809,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -9832,7 +9830,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -9849,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -9870,7 +9868,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -9887,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -9908,7 +9906,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -9925,7 +9923,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -9946,7 +9944,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -9963,7 +9961,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -10001,7 +9999,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -10022,7 +10020,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -10039,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -10060,7 +10058,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -10077,7 +10075,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -10098,7 +10096,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -10115,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -10136,7 +10134,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -10153,7 +10151,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -10174,7 +10172,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -10191,7 +10189,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -10212,7 +10210,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -10229,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -10250,7 +10248,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -10267,7 +10265,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -10288,7 +10286,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -10305,7 +10303,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -10326,7 +10324,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -10343,7 +10341,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -10364,7 +10362,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -10381,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -10402,7 +10400,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -10419,7 +10417,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -10440,7 +10438,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -10457,7 +10455,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -10478,7 +10476,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -10495,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -10516,7 +10514,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -10533,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -10554,7 +10552,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -10571,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -10592,7 +10590,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -10609,7 +10607,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -10630,7 +10628,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -10647,7 +10645,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -10668,7 +10666,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -10685,7 +10683,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -10706,7 +10704,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -10723,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -10744,7 +10742,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -10761,7 +10759,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -10782,7 +10780,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -10799,7 +10797,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -10820,7 +10818,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -10837,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -10856,7 +10854,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -10873,7 +10871,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -10892,7 +10890,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -10909,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -10928,7 +10926,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -10945,7 +10943,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -11164,7 +11162,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -11185,7 +11183,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -11202,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -11223,7 +11221,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -11240,7 +11238,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -11261,7 +11259,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -11278,7 +11276,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -11299,7 +11297,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -11316,7 +11314,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -11354,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -11375,7 +11373,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -11392,7 +11390,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -11413,7 +11411,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -11430,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -11451,7 +11449,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -11468,7 +11466,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -11489,7 +11487,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -11506,7 +11504,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -11527,7 +11525,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -11544,7 +11542,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -11565,7 +11563,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -11582,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -11603,7 +11601,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -11620,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -11641,7 +11639,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -11658,7 +11656,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -11679,7 +11677,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -11696,7 +11694,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -11717,7 +11715,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -11734,7 +11732,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -11755,7 +11753,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -11772,7 +11770,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -11793,7 +11791,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -11810,7 +11808,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -11831,7 +11829,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -11848,7 +11846,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -11869,7 +11867,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -11886,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -11907,7 +11905,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -11924,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -11945,7 +11943,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -11962,7 +11960,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -11983,7 +11981,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -12000,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -12021,7 +12019,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -12038,7 +12036,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -12059,7 +12057,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -12076,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -12097,7 +12095,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -12114,7 +12112,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -12135,7 +12133,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -12152,7 +12150,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -12173,7 +12171,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -12190,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -12209,7 +12207,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -12226,7 +12224,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -12245,7 +12243,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -12262,7 +12260,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -12281,7 +12279,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -12298,7 +12296,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -12517,7 +12515,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -12538,7 +12536,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -12555,7 +12553,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -12576,7 +12574,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -12593,7 +12591,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -12614,7 +12612,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -12631,7 +12629,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -12652,7 +12650,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -12669,7 +12667,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -12707,7 +12705,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -12728,7 +12726,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -12745,7 +12743,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -12766,7 +12764,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -12783,7 +12781,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -12804,7 +12802,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -12821,7 +12819,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -12842,7 +12840,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -12859,7 +12857,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -12880,7 +12878,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -12897,7 +12895,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -12918,7 +12916,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -12935,7 +12933,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -12956,7 +12954,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -12973,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -12994,7 +12992,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -13011,7 +13009,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -13032,7 +13030,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -13049,7 +13047,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -13070,7 +13068,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -13087,7 +13085,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -13108,7 +13106,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -13125,7 +13123,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -13146,7 +13144,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -13163,7 +13161,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -13184,7 +13182,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -13201,7 +13199,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -13222,7 +13220,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -13239,7 +13237,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -13260,7 +13258,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -13277,7 +13275,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -13298,7 +13296,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -13315,7 +13313,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -13336,7 +13334,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -13352,12 +13350,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="30">
-        <v>2.0833333333333332E-2</v>
+      <c r="K24" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L24" s="1">
         <f t="shared" si="4"/>
-        <v>-2.0833333333333332E-2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="1">
         <f t="shared" si="5"/>
@@ -13373,7 +13372,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -13389,7 +13388,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -13410,7 +13410,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -13427,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -13448,7 +13448,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -13465,7 +13465,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -13486,7 +13486,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -13503,7 +13503,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -13524,7 +13524,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -13540,12 +13540,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K29" s="30">
-        <v>2.0833333333333332E-2</v>
+      <c r="K29" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" si="4"/>
-        <v>-2.0833333333333332E-2</v>
+        <v>0</v>
       </c>
       <c r="M29" s="1">
         <f t="shared" si="5"/>
@@ -13559,7 +13560,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -13576,7 +13577,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -13595,7 +13596,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -13612,7 +13613,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -13631,7 +13632,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -13648,7 +13649,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -13671,10 +13672,10 @@
       <c r="B33" s="27">
         <v>0</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="34"/>
+      <c r="D33" s="33"/>
       <c r="E33" s="27" t="s">
         <v>26</v>
       </c>
@@ -13715,11 +13716,11 @@
       </c>
       <c r="K34" s="2">
         <f>SUM(K2:K32)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="13">
         <f>SUM(L2:L32)</f>
-        <v>-4.1666666666666664E-2</v>
+        <v>0</v>
       </c>
       <c r="M34" s="22">
         <f>SUM(M2:M32)</f>
@@ -13733,7 +13734,7 @@
     <row r="36" spans="1:14" ht="18.600000000000001" thickBot="1">
       <c r="L36" s="2">
         <f>L34*12/52</f>
-        <v>-9.6153846153846159E-3</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>19</v>
@@ -13884,7 +13885,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K6" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -13905,7 +13906,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -13921,19 +13922,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K3" s="30">
+      <c r="K3" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
-        <f t="shared" ref="L3:L32" si="3">J3-K3</f>
+        <f t="shared" ref="L3:L32" si="4">J3-K3</f>
         <v>0</v>
       </c>
       <c r="M3" s="1">
-        <f t="shared" ref="M3:M32" si="4">IF(L3&gt;=TIME(8,0,0),L3-TIME(8,0,0),0)</f>
+        <f t="shared" ref="M3:M32" si="5">IF(L3&gt;=TIME(8,0,0),L3-TIME(8,0,0),0)</f>
         <v>0</v>
       </c>
       <c r="N3" s="1">
-        <f t="shared" ref="N3:N32" si="5">"5:00"-MIN(C3,"5:00")+MAX((F3&lt;C3)+F3,"22:00")-"22:00"</f>
+        <f t="shared" ref="N3:N32" si="6">"5:00"-MIN(C3,"5:00")+MAX((F3&lt;C3)+F3,"22:00")-"22:00"</f>
         <v>0</v>
       </c>
     </row>
@@ -13942,7 +13944,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -13959,19 +13961,19 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" ref="K4:K6" si="6">IF(J4&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M4" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -13980,7 +13982,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -13997,19 +13999,19 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M5" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N5" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14018,7 +14020,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -14035,19 +14037,19 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14077,15 +14079,15 @@
         <v>0</v>
       </c>
       <c r="L7" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N7" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14094,7 +14096,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -14115,15 +14117,15 @@
         <v>0</v>
       </c>
       <c r="L8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N8" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14132,7 +14134,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -14153,15 +14155,15 @@
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N9" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14170,7 +14172,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -14191,15 +14193,15 @@
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14208,7 +14210,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -14229,15 +14231,15 @@
         <v>0</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14246,7 +14248,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -14267,15 +14269,15 @@
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14284,7 +14286,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -14300,19 +14302,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="30">
-        <v>6.9444444444444441E-3</v>
+      <c r="K13" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="3"/>
-        <v>-6.9444444444444441E-3</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N13" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14321,7 +14324,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -14342,15 +14345,15 @@
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N14" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14359,7 +14362,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -14380,15 +14383,15 @@
         <v>0</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14397,7 +14400,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -14418,15 +14421,15 @@
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14435,7 +14438,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -14456,15 +14459,15 @@
         <v>0</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14473,7 +14476,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -14494,15 +14497,15 @@
         <v>0</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M18" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14511,7 +14514,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -14532,15 +14535,15 @@
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M19" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N19" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14549,7 +14552,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -14570,15 +14573,15 @@
         <v>0</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14587,7 +14590,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -14608,15 +14611,15 @@
         <v>0</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N21" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14625,7 +14628,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -14646,15 +14649,15 @@
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14663,7 +14666,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -14684,15 +14687,15 @@
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14701,7 +14704,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -14722,15 +14725,15 @@
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14739,7 +14742,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -14760,15 +14763,15 @@
         <v>0</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M25" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14777,7 +14780,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -14798,15 +14801,15 @@
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M26" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14815,7 +14818,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -14836,15 +14839,15 @@
         <v>0</v>
       </c>
       <c r="L27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N27" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14853,7 +14856,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -14874,15 +14877,15 @@
         <v>0</v>
       </c>
       <c r="L28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N28" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -14891,7 +14894,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -14912,22 +14915,22 @@
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N29" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -14948,22 +14951,22 @@
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M30" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N30" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -14984,22 +14987,22 @@
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N31" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -15020,15 +15023,15 @@
         <v>0</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N32" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -15039,10 +15042,10 @@
       <c r="B33" s="27">
         <v>0</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="34"/>
+      <c r="D33" s="33"/>
       <c r="E33" s="27" t="s">
         <v>26</v>
       </c>
@@ -15082,11 +15085,11 @@
       </c>
       <c r="K34" s="2">
         <f>SUM(K2:K32)</f>
-        <v>6.9444444444444441E-3</v>
+        <v>0</v>
       </c>
       <c r="L34" s="13">
         <f>SUM(L2:L32)</f>
-        <v>-6.9444444444444441E-3</v>
+        <v>0</v>
       </c>
       <c r="M34" s="22">
         <f>SUM(M2:M32)</f>
@@ -15100,7 +15103,7 @@
     <row r="36" spans="1:14" ht="18.600000000000001" thickBot="1">
       <c r="L36" s="2">
         <f>L34*12/52</f>
-        <v>-1.6025641025641025E-3</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>19</v>
@@ -15251,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -15272,7 +15275,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -15289,7 +15292,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -15310,7 +15313,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -15327,7 +15330,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -15348,7 +15351,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -15365,7 +15368,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -15386,7 +15389,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -15403,7 +15406,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -15441,7 +15444,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -15462,7 +15465,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -15479,7 +15482,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -15500,7 +15503,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -15517,7 +15520,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -15538,7 +15541,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -15555,7 +15558,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -15576,7 +15579,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -15593,7 +15596,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -15614,7 +15617,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -15631,7 +15634,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -15652,7 +15655,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -15669,7 +15672,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -15690,7 +15693,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -15707,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -15728,7 +15731,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -15745,7 +15748,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -15766,7 +15769,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -15783,7 +15786,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -15804,7 +15807,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -15821,7 +15824,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -15842,7 +15845,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -15859,7 +15862,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -15880,7 +15883,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -15897,7 +15900,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -15918,7 +15921,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -15935,7 +15938,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -15956,7 +15959,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -15973,7 +15976,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -15994,7 +15997,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -16011,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -16032,7 +16035,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -16049,7 +16052,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -16070,7 +16073,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -16087,7 +16090,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -16108,7 +16111,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -16125,7 +16128,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -16146,7 +16149,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -16163,7 +16166,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -16184,7 +16187,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -16201,7 +16204,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -16222,7 +16225,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -16239,7 +16242,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -16260,7 +16263,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -16277,7 +16280,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -16296,7 +16299,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -16313,7 +16316,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -16332,7 +16335,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -16349,7 +16352,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -16368,7 +16371,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -16385,7 +16388,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -16402,10 +16405,10 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="18.600000000000001" thickBot="1">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="27">
         <v>1500</v>
       </c>
@@ -16437,8 +16440,8 @@
       </c>
     </row>
     <row r="34" spans="1:14" ht="18.600000000000001" thickBot="1">
-      <c r="A34" s="35"/>
-      <c r="B34" s="35"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="27">
         <v>1226</v>
       </c>
@@ -16480,8 +16483,8 @@
       </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="35"/>
-      <c r="B35" s="35"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="27">
         <v>1000</v>
       </c>
@@ -16494,8 +16497,8 @@
       </c>
     </row>
     <row r="36" spans="1:14" ht="18.600000000000001" thickBot="1">
-      <c r="A36" s="35"/>
-      <c r="B36" s="35"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
@@ -16511,8 +16514,8 @@
       </c>
     </row>
     <row r="37" spans="1:14" ht="18.600000000000001" thickBot="1">
-      <c r="A37" s="35"/>
-      <c r="B37" s="35"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
@@ -16528,12 +16531,12 @@
       </c>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="35"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="31" t="s">
+      <c r="A38" s="34"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="32"/>
+      <c r="D38" s="31"/>
       <c r="E38" s="27">
         <f>SUM(E33:E37)</f>
         <v>9952</v>
@@ -16668,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -16689,7 +16692,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -16706,7 +16709,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -16727,7 +16730,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -16743,7 +16746,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="8">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -16764,7 +16768,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -16781,7 +16785,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -16802,7 +16806,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -16819,7 +16823,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -16857,7 +16861,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -16878,7 +16882,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -16895,7 +16899,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -16916,7 +16920,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -16933,7 +16937,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -16954,7 +16958,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -16971,7 +16975,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -16992,7 +16996,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -17009,7 +17013,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -17030,7 +17034,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -17047,7 +17051,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -17068,7 +17072,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -17085,7 +17089,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -17106,7 +17110,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -17123,7 +17127,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -17144,7 +17148,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -17161,7 +17165,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -17182,7 +17186,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -17199,7 +17203,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -17220,7 +17224,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -17237,7 +17241,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -17258,7 +17262,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -17275,7 +17279,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -17296,7 +17300,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -17313,7 +17317,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -17334,7 +17338,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -17351,7 +17355,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -17372,7 +17376,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -17389,7 +17393,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -17410,7 +17414,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -17427,7 +17431,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -17448,7 +17452,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -17465,7 +17469,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="1">
@@ -17486,7 +17490,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -17503,7 +17507,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -17524,7 +17528,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -17541,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -17562,7 +17566,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -17579,7 +17583,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -17600,7 +17604,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -17617,7 +17621,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -17638,7 +17642,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -17655,7 +17659,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -17676,7 +17680,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -17693,7 +17697,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -17712,7 +17716,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -17729,7 +17733,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -17748,7 +17752,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -17765,7 +17769,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -17784,7 +17788,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -17801,7 +17805,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -18021,7 +18025,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" ref="K2:K32" si="2">IF(J2&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="1">
@@ -18042,7 +18046,7 @@
         <v>46055</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B32" si="2">TEXT(A3, "aaa")</f>
+        <f t="shared" ref="B3:B32" si="3">TEXT(A3, "aaa")</f>
         <v>月</v>
       </c>
       <c r="C3" s="11"/>
@@ -18059,7 +18063,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f t="shared" ref="K3:K32" si="3">IF(J3&gt;TIME(5,59,0),TIME(0,45,0),0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L3" s="1">
@@ -18080,7 +18084,7 @@
         <v>46056</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C4" s="11"/>
@@ -18097,7 +18101,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L4" s="1">
@@ -18118,7 +18122,7 @@
         <v>46057</v>
       </c>
       <c r="B5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C5" s="12"/>
@@ -18135,7 +18139,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L5" s="1">
@@ -18156,7 +18160,7 @@
         <v>46058</v>
       </c>
       <c r="B6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C6" s="11"/>
@@ -18173,7 +18177,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="1">
@@ -18211,7 +18215,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1">
@@ -18232,7 +18236,7 @@
         <v>46060</v>
       </c>
       <c r="B8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C8" s="11"/>
@@ -18249,7 +18253,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1">
@@ -18270,7 +18274,7 @@
         <v>46061</v>
       </c>
       <c r="B9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C9" s="11"/>
@@ -18287,7 +18291,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1">
@@ -18308,7 +18312,7 @@
         <v>46062</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C10" s="11"/>
@@ -18325,7 +18329,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L10" s="1">
@@ -18346,7 +18350,7 @@
         <v>46063</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C11" s="11"/>
@@ -18363,7 +18367,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L11" s="1">
@@ -18384,7 +18388,7 @@
         <v>46064</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C12" s="11"/>
@@ -18401,7 +18405,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1">
@@ -18422,7 +18426,7 @@
         <v>46065</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C13" s="11"/>
@@ -18439,7 +18443,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1">
@@ -18460,7 +18464,7 @@
         <v>46066</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C14" s="11"/>
@@ -18477,7 +18481,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="1">
@@ -18498,7 +18502,7 @@
         <v>46067</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C15" s="11"/>
@@ -18515,7 +18519,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="1">
@@ -18536,7 +18540,7 @@
         <v>46068</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C16" s="11"/>
@@ -18553,7 +18557,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="1">
@@ -18574,7 +18578,7 @@
         <v>46069</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C17" s="11"/>
@@ -18591,7 +18595,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="1">
@@ -18612,7 +18616,7 @@
         <v>46070</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C18" s="11"/>
@@ -18629,7 +18633,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="1">
@@ -18650,7 +18654,7 @@
         <v>46071</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C19" s="11"/>
@@ -18667,7 +18671,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="1">
@@ -18688,7 +18692,7 @@
         <v>46072</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C20" s="11"/>
@@ -18705,7 +18709,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="1">
@@ -18726,7 +18730,7 @@
         <v>46073</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C21" s="11"/>
@@ -18743,7 +18747,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="1">
@@ -18764,7 +18768,7 @@
         <v>46074</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C22" s="11"/>
@@ -18781,7 +18785,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="1">
@@ -18802,7 +18806,7 @@
         <v>46075</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>日</v>
       </c>
       <c r="C23" s="11"/>
@@ -18818,12 +18822,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K23" s="30">
-        <v>2.0833333333333332E-2</v>
+      <c r="K23" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L23" s="1">
         <f t="shared" si="4"/>
-        <v>-2.0833333333333332E-2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="1">
         <f t="shared" si="5"/>
@@ -18839,7 +18844,7 @@
         <v>46076</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>月</v>
       </c>
       <c r="C24" s="11"/>
@@ -18856,7 +18861,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="1">
@@ -18877,7 +18882,7 @@
         <v>46077</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>火</v>
       </c>
       <c r="C25" s="11"/>
@@ -18894,7 +18899,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="1">
@@ -18915,7 +18920,7 @@
         <v>46078</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>水</v>
       </c>
       <c r="C26" s="11"/>
@@ -18932,7 +18937,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L26" s="1">
@@ -18953,7 +18958,7 @@
         <v>46079</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>木</v>
       </c>
       <c r="C27" s="11"/>
@@ -18970,7 +18975,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L27" s="1">
@@ -18991,7 +18996,7 @@
         <v>46080</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>金</v>
       </c>
       <c r="C28" s="11"/>
@@ -19008,7 +19013,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="1">
@@ -19029,7 +19034,7 @@
         <v>46081</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C29" s="11"/>
@@ -19046,7 +19051,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="1">
@@ -19065,7 +19070,7 @@
     <row r="30" spans="1:14">
       <c r="A30" s="18"/>
       <c r="B30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C30" s="11"/>
@@ -19082,7 +19087,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="1">
@@ -19101,7 +19106,7 @@
     <row r="31" spans="1:14">
       <c r="A31" s="18"/>
       <c r="B31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C31" s="11"/>
@@ -19118,7 +19123,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="1">
@@ -19137,7 +19142,7 @@
     <row r="32" spans="1:14">
       <c r="A32" s="18"/>
       <c r="B32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>土</v>
       </c>
       <c r="C32" s="11"/>
@@ -19154,7 +19159,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="1">
@@ -19177,10 +19182,10 @@
       <c r="B33" s="27">
         <v>0</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="34"/>
+      <c r="D33" s="33"/>
       <c r="E33" s="27" t="s">
         <v>23</v>
       </c>
@@ -19228,11 +19233,11 @@
       </c>
       <c r="K34" s="2">
         <f>SUM(K2:K32)</f>
-        <v>2.0833333333333332E-2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="13">
         <f>SUM(L2:L32)</f>
-        <v>-2.0833333333333332E-2</v>
+        <v>0</v>
       </c>
       <c r="M34" s="22">
         <f>SUM(M2:M32)</f>
@@ -19249,7 +19254,7 @@
     <row r="36" spans="1:14" ht="18.600000000000001" thickBot="1">
       <c r="L36" s="2">
         <f>L34*12/52</f>
-        <v>-4.807692307692308E-3</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>19</v>
